--- a/Python/dz2/work/output/medical_records.xlsx
+++ b/Python/dz2/work/output/medical_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>record_date</t>
   </si>
@@ -40,16 +40,46 @@
     <t>comment</t>
   </si>
   <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>Бим</t>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>Барсик</t>
+  </si>
+  <si>
+    <t>Тиша</t>
+  </si>
+  <si>
+    <t>Лорд</t>
+  </si>
+  <si>
+    <t>Том</t>
+  </si>
+  <si>
+    <t>Кошка</t>
   </si>
   <si>
     <t>Собака</t>
   </si>
   <si>
-    <t>На лечении</t>
+    <t>В приюте</t>
+  </si>
+  <si>
+    <t>Пристроено</t>
+  </si>
+  <si>
+    <t>Готов к пристройству</t>
   </si>
   <si>
     <t>Дерматит</t>
@@ -61,7 +91,7 @@
     <t>Сергеев А.А.</t>
   </si>
   <si>
-    <t>Наблюдается улучшение</t>
+    <t>Контроль через 10 дней</t>
   </si>
 </sst>
 </file>
@@ -419,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -453,25 +483,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
